--- a/demo/demo4-complete/poc-output/templates/cl-selections-template.xlsx
+++ b/demo/demo4-complete/poc-output/templates/cl-selections-template.xlsx
@@ -29,6 +29,13 @@
     <sheet name="Sel Ults - Paid Loss" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Sel Ults - Reported Count" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Sel Ults - Closed Count" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Ult Severity" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="X-to-Ult Incurred" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="X-to-Ult Paid" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="X-to-Ult Reported" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="X-to-Ult Closed" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Avg IBNR" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Avg Unpaid" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -174,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,6 +248,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8936,6 +8944,3502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Ultimate Severity — Incurred / Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>Incurred Ultimate</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>Reported Ultimate</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="inlineStr">
+        <is>
+          <t>Ultimate Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Sel Ults - Incurred Loss'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="27">
+        <f>'Sel Ults - Incurred Loss'!D3</f>
+        <v/>
+      </c>
+      <c r="C3" s="27">
+        <f>'Sel Ults - Reported Count'!D3</f>
+        <v/>
+      </c>
+      <c r="D3" s="32">
+        <f>IFERROR(B3/C3,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Sel Ults - Incurred Loss'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="27">
+        <f>'Sel Ults - Incurred Loss'!D4</f>
+        <v/>
+      </c>
+      <c r="C4" s="27">
+        <f>'Sel Ults - Reported Count'!D4</f>
+        <v/>
+      </c>
+      <c r="D4" s="32">
+        <f>IFERROR(B4/C4,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Sel Ults - Incurred Loss'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="27">
+        <f>'Sel Ults - Incurred Loss'!D5</f>
+        <v/>
+      </c>
+      <c r="C5" s="27">
+        <f>'Sel Ults - Reported Count'!D5</f>
+        <v/>
+      </c>
+      <c r="D5" s="32">
+        <f>IFERROR(B5/C5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Sel Ults - Incurred Loss'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="27">
+        <f>'Sel Ults - Incurred Loss'!D6</f>
+        <v/>
+      </c>
+      <c r="C6" s="27">
+        <f>'Sel Ults - Reported Count'!D6</f>
+        <v/>
+      </c>
+      <c r="D6" s="32">
+        <f>IFERROR(B6/C6,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Sel Ults - Incurred Loss'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="27">
+        <f>'Sel Ults - Incurred Loss'!D7</f>
+        <v/>
+      </c>
+      <c r="C7" s="27">
+        <f>'Sel Ults - Reported Count'!D7</f>
+        <v/>
+      </c>
+      <c r="D7" s="32">
+        <f>IFERROR(B7/C7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Sel Ults - Incurred Loss'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="27">
+        <f>'Sel Ults - Incurred Loss'!D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
+        <f>'Sel Ults - Reported Count'!D8</f>
+        <v/>
+      </c>
+      <c r="D8" s="32">
+        <f>IFERROR(B8/C8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Sel Ults - Incurred Loss'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="27">
+        <f>'Sel Ults - Incurred Loss'!D9</f>
+        <v/>
+      </c>
+      <c r="C9" s="27">
+        <f>'Sel Ults - Reported Count'!D9</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>IFERROR(B9/C9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Sel Ults - Incurred Loss'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="27">
+        <f>'Sel Ults - Incurred Loss'!D10</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>'Sel Ults - Reported Count'!D10</f>
+        <v/>
+      </c>
+      <c r="D10" s="32">
+        <f>IFERROR(B10/C10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Sel Ults - Incurred Loss'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="27">
+        <f>'Sel Ults - Incurred Loss'!D11</f>
+        <v/>
+      </c>
+      <c r="C11" s="27">
+        <f>'Sel Ults - Reported Count'!D11</f>
+        <v/>
+      </c>
+      <c r="D11" s="32">
+        <f>IFERROR(B11/C11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Sel Ults - Incurred Loss'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="27">
+        <f>'Sel Ults - Incurred Loss'!D12</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>'Sel Ults - Reported Count'!D12</f>
+        <v/>
+      </c>
+      <c r="D12" s="32">
+        <f>IFERROR(B12/C12,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Incurred to Ultimate — ratio triangle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29">
+        <f>'Incurred Loss'!B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="29">
+        <f>'Incurred Loss'!C$2</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>'Incurred Loss'!D$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>'Incurred Loss'!E$2</f>
+        <v/>
+      </c>
+      <c r="F2" s="29">
+        <f>'Incurred Loss'!F$2</f>
+        <v/>
+      </c>
+      <c r="G2" s="29">
+        <f>'Incurred Loss'!G$2</f>
+        <v/>
+      </c>
+      <c r="H2" s="29">
+        <f>'Incurred Loss'!H$2</f>
+        <v/>
+      </c>
+      <c r="I2" s="29">
+        <f>'Incurred Loss'!I$2</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>'Incurred Loss'!J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>'Incurred Loss'!K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Incurred Loss'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B3="","",'Incurred Loss'!B3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C3="","",'Incurred Loss'!C3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D3="","",'Incurred Loss'!D3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E3="","",'Incurred Loss'!E3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F3="","",'Incurred Loss'!F3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G3="","",'Incurred Loss'!G3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H3="","",'Incurred Loss'!H3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I3="","",'Incurred Loss'!I3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J3="","",'Incurred Loss'!J3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K3="","",'Incurred Loss'!K3/'Sel Ults - Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Incurred Loss'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B4="","",'Incurred Loss'!B4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C4="","",'Incurred Loss'!C4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D4="","",'Incurred Loss'!D4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E4="","",'Incurred Loss'!E4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F4="","",'Incurred Loss'!F4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G4="","",'Incurred Loss'!G4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H4="","",'Incurred Loss'!H4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I4="","",'Incurred Loss'!I4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J4="","",'Incurred Loss'!J4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K4="","",'Incurred Loss'!K4/'Sel Ults - Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Incurred Loss'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B5="","",'Incurred Loss'!B5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C5="","",'Incurred Loss'!C5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D5="","",'Incurred Loss'!D5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E5="","",'Incurred Loss'!E5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F5="","",'Incurred Loss'!F5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G5="","",'Incurred Loss'!G5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H5="","",'Incurred Loss'!H5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I5="","",'Incurred Loss'!I5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J5="","",'Incurred Loss'!J5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K5="","",'Incurred Loss'!K5/'Sel Ults - Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Incurred Loss'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B6="","",'Incurred Loss'!B6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C6="","",'Incurred Loss'!C6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D6="","",'Incurred Loss'!D6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E6="","",'Incurred Loss'!E6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F6="","",'Incurred Loss'!F6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G6="","",'Incurred Loss'!G6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H6="","",'Incurred Loss'!H6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I6="","",'Incurred Loss'!I6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J6="","",'Incurred Loss'!J6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K6="","",'Incurred Loss'!K6/'Sel Ults - Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Incurred Loss'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B7="","",'Incurred Loss'!B7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C7="","",'Incurred Loss'!C7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D7="","",'Incurred Loss'!D7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E7="","",'Incurred Loss'!E7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F7="","",'Incurred Loss'!F7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G7="","",'Incurred Loss'!G7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H7="","",'Incurred Loss'!H7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I7="","",'Incurred Loss'!I7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J7="","",'Incurred Loss'!J7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K7="","",'Incurred Loss'!K7/'Sel Ults - Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Incurred Loss'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B8="","",'Incurred Loss'!B8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C8="","",'Incurred Loss'!C8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D8="","",'Incurred Loss'!D8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E8="","",'Incurred Loss'!E8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F8="","",'Incurred Loss'!F8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G8="","",'Incurred Loss'!G8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H8="","",'Incurred Loss'!H8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I8="","",'Incurred Loss'!I8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J8="","",'Incurred Loss'!J8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K8="","",'Incurred Loss'!K8/'Sel Ults - Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Incurred Loss'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B9="","",'Incurred Loss'!B9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C9="","",'Incurred Loss'!C9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D9="","",'Incurred Loss'!D9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E9="","",'Incurred Loss'!E9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F9="","",'Incurred Loss'!F9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G9="","",'Incurred Loss'!G9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H9="","",'Incurred Loss'!H9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I9="","",'Incurred Loss'!I9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J9="","",'Incurred Loss'!J9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K9="","",'Incurred Loss'!K9/'Sel Ults - Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Incurred Loss'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B10="","",'Incurred Loss'!B10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C10="","",'Incurred Loss'!C10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D10="","",'Incurred Loss'!D10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E10="","",'Incurred Loss'!E10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F10="","",'Incurred Loss'!F10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G10="","",'Incurred Loss'!G10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H10="","",'Incurred Loss'!H10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I10="","",'Incurred Loss'!I10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J10="","",'Incurred Loss'!J10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K10="","",'Incurred Loss'!K10/'Sel Ults - Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Incurred Loss'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B11="","",'Incurred Loss'!B11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C11="","",'Incurred Loss'!C11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D11="","",'Incurred Loss'!D11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E11="","",'Incurred Loss'!E11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F11="","",'Incurred Loss'!F11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G11="","",'Incurred Loss'!G11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H11="","",'Incurred Loss'!H11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I11="","",'Incurred Loss'!I11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J11="","",'Incurred Loss'!J11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K11="","",'Incurred Loss'!K11/'Sel Ults - Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Incurred Loss'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!B12="","",'Incurred Loss'!B12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!C12="","",'Incurred Loss'!C12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!D12="","",'Incurred Loss'!D12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!E12="","",'Incurred Loss'!E12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!F12="","",'Incurred Loss'!F12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!G12="","",'Incurred Loss'!G12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!H12="","",'Incurred Loss'!H12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!I12="","",'Incurred Loss'!I12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!J12="","",'Incurred Loss'!J12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="25">
+        <f>IFERROR(IF('Incurred Loss'!K12="","",'Incurred Loss'!K12/'Sel Ults - Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Paid to Ultimate — ratio triangle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29">
+        <f>'Paid Loss'!B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="29">
+        <f>'Paid Loss'!C$2</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>'Paid Loss'!D$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>'Paid Loss'!E$2</f>
+        <v/>
+      </c>
+      <c r="F2" s="29">
+        <f>'Paid Loss'!F$2</f>
+        <v/>
+      </c>
+      <c r="G2" s="29">
+        <f>'Paid Loss'!G$2</f>
+        <v/>
+      </c>
+      <c r="H2" s="29">
+        <f>'Paid Loss'!H$2</f>
+        <v/>
+      </c>
+      <c r="I2" s="29">
+        <f>'Paid Loss'!I$2</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>'Paid Loss'!J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>'Paid Loss'!K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Paid Loss'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="25">
+        <f>IFERROR(IF('Paid Loss'!B3="","",'Paid Loss'!B3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="25">
+        <f>IFERROR(IF('Paid Loss'!C3="","",'Paid Loss'!C3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="25">
+        <f>IFERROR(IF('Paid Loss'!D3="","",'Paid Loss'!D3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="25">
+        <f>IFERROR(IF('Paid Loss'!E3="","",'Paid Loss'!E3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="25">
+        <f>IFERROR(IF('Paid Loss'!F3="","",'Paid Loss'!F3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="25">
+        <f>IFERROR(IF('Paid Loss'!G3="","",'Paid Loss'!G3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="25">
+        <f>IFERROR(IF('Paid Loss'!H3="","",'Paid Loss'!H3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="25">
+        <f>IFERROR(IF('Paid Loss'!I3="","",'Paid Loss'!I3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="25">
+        <f>IFERROR(IF('Paid Loss'!J3="","",'Paid Loss'!J3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="25">
+        <f>IFERROR(IF('Paid Loss'!K3="","",'Paid Loss'!K3/'Sel Ults - Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Paid Loss'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="25">
+        <f>IFERROR(IF('Paid Loss'!B4="","",'Paid Loss'!B4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="25">
+        <f>IFERROR(IF('Paid Loss'!C4="","",'Paid Loss'!C4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="25">
+        <f>IFERROR(IF('Paid Loss'!D4="","",'Paid Loss'!D4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="25">
+        <f>IFERROR(IF('Paid Loss'!E4="","",'Paid Loss'!E4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="25">
+        <f>IFERROR(IF('Paid Loss'!F4="","",'Paid Loss'!F4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="25">
+        <f>IFERROR(IF('Paid Loss'!G4="","",'Paid Loss'!G4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="25">
+        <f>IFERROR(IF('Paid Loss'!H4="","",'Paid Loss'!H4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="25">
+        <f>IFERROR(IF('Paid Loss'!I4="","",'Paid Loss'!I4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="25">
+        <f>IFERROR(IF('Paid Loss'!J4="","",'Paid Loss'!J4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="25">
+        <f>IFERROR(IF('Paid Loss'!K4="","",'Paid Loss'!K4/'Sel Ults - Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Paid Loss'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="25">
+        <f>IFERROR(IF('Paid Loss'!B5="","",'Paid Loss'!B5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="25">
+        <f>IFERROR(IF('Paid Loss'!C5="","",'Paid Loss'!C5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="25">
+        <f>IFERROR(IF('Paid Loss'!D5="","",'Paid Loss'!D5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="25">
+        <f>IFERROR(IF('Paid Loss'!E5="","",'Paid Loss'!E5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="25">
+        <f>IFERROR(IF('Paid Loss'!F5="","",'Paid Loss'!F5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="25">
+        <f>IFERROR(IF('Paid Loss'!G5="","",'Paid Loss'!G5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25">
+        <f>IFERROR(IF('Paid Loss'!H5="","",'Paid Loss'!H5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="25">
+        <f>IFERROR(IF('Paid Loss'!I5="","",'Paid Loss'!I5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="25">
+        <f>IFERROR(IF('Paid Loss'!J5="","",'Paid Loss'!J5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
+        <f>IFERROR(IF('Paid Loss'!K5="","",'Paid Loss'!K5/'Sel Ults - Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Paid Loss'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="25">
+        <f>IFERROR(IF('Paid Loss'!B6="","",'Paid Loss'!B6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="25">
+        <f>IFERROR(IF('Paid Loss'!C6="","",'Paid Loss'!C6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="25">
+        <f>IFERROR(IF('Paid Loss'!D6="","",'Paid Loss'!D6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IFERROR(IF('Paid Loss'!E6="","",'Paid Loss'!E6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>IFERROR(IF('Paid Loss'!F6="","",'Paid Loss'!F6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>IFERROR(IF('Paid Loss'!G6="","",'Paid Loss'!G6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>IFERROR(IF('Paid Loss'!H6="","",'Paid Loss'!H6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="25">
+        <f>IFERROR(IF('Paid Loss'!I6="","",'Paid Loss'!I6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="25">
+        <f>IFERROR(IF('Paid Loss'!J6="","",'Paid Loss'!J6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
+        <f>IFERROR(IF('Paid Loss'!K6="","",'Paid Loss'!K6/'Sel Ults - Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Paid Loss'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="25">
+        <f>IFERROR(IF('Paid Loss'!B7="","",'Paid Loss'!B7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>IFERROR(IF('Paid Loss'!C7="","",'Paid Loss'!C7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>IFERROR(IF('Paid Loss'!D7="","",'Paid Loss'!D7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>IFERROR(IF('Paid Loss'!E7="","",'Paid Loss'!E7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>IFERROR(IF('Paid Loss'!F7="","",'Paid Loss'!F7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>IFERROR(IF('Paid Loss'!G7="","",'Paid Loss'!G7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>IFERROR(IF('Paid Loss'!H7="","",'Paid Loss'!H7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="25">
+        <f>IFERROR(IF('Paid Loss'!I7="","",'Paid Loss'!I7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>IFERROR(IF('Paid Loss'!J7="","",'Paid Loss'!J7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>IFERROR(IF('Paid Loss'!K7="","",'Paid Loss'!K7/'Sel Ults - Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Paid Loss'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="25">
+        <f>IFERROR(IF('Paid Loss'!B8="","",'Paid Loss'!B8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="25">
+        <f>IFERROR(IF('Paid Loss'!C8="","",'Paid Loss'!C8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>IFERROR(IF('Paid Loss'!D8="","",'Paid Loss'!D8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IFERROR(IF('Paid Loss'!E8="","",'Paid Loss'!E8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>IFERROR(IF('Paid Loss'!F8="","",'Paid Loss'!F8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>IFERROR(IF('Paid Loss'!G8="","",'Paid Loss'!G8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IFERROR(IF('Paid Loss'!H8="","",'Paid Loss'!H8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>IFERROR(IF('Paid Loss'!I8="","",'Paid Loss'!I8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>IFERROR(IF('Paid Loss'!J8="","",'Paid Loss'!J8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
+        <f>IFERROR(IF('Paid Loss'!K8="","",'Paid Loss'!K8/'Sel Ults - Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Paid Loss'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="25">
+        <f>IFERROR(IF('Paid Loss'!B9="","",'Paid Loss'!B9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>IFERROR(IF('Paid Loss'!C9="","",'Paid Loss'!C9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
+        <f>IFERROR(IF('Paid Loss'!D9="","",'Paid Loss'!D9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>IFERROR(IF('Paid Loss'!E9="","",'Paid Loss'!E9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>IFERROR(IF('Paid Loss'!F9="","",'Paid Loss'!F9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>IFERROR(IF('Paid Loss'!G9="","",'Paid Loss'!G9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>IFERROR(IF('Paid Loss'!H9="","",'Paid Loss'!H9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>IFERROR(IF('Paid Loss'!I9="","",'Paid Loss'!I9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="25">
+        <f>IFERROR(IF('Paid Loss'!J9="","",'Paid Loss'!J9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>IFERROR(IF('Paid Loss'!K9="","",'Paid Loss'!K9/'Sel Ults - Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Paid Loss'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="25">
+        <f>IFERROR(IF('Paid Loss'!B10="","",'Paid Loss'!B10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="25">
+        <f>IFERROR(IF('Paid Loss'!C10="","",'Paid Loss'!C10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="25">
+        <f>IFERROR(IF('Paid Loss'!D10="","",'Paid Loss'!D10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>IFERROR(IF('Paid Loss'!E10="","",'Paid Loss'!E10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>IFERROR(IF('Paid Loss'!F10="","",'Paid Loss'!F10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>IFERROR(IF('Paid Loss'!G10="","",'Paid Loss'!G10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>IFERROR(IF('Paid Loss'!H10="","",'Paid Loss'!H10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="25">
+        <f>IFERROR(IF('Paid Loss'!I10="","",'Paid Loss'!I10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="25">
+        <f>IFERROR(IF('Paid Loss'!J10="","",'Paid Loss'!J10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="25">
+        <f>IFERROR(IF('Paid Loss'!K10="","",'Paid Loss'!K10/'Sel Ults - Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Paid Loss'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="25">
+        <f>IFERROR(IF('Paid Loss'!B11="","",'Paid Loss'!B11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>IFERROR(IF('Paid Loss'!C11="","",'Paid Loss'!C11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="25">
+        <f>IFERROR(IF('Paid Loss'!D11="","",'Paid Loss'!D11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>IFERROR(IF('Paid Loss'!E11="","",'Paid Loss'!E11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
+        <f>IFERROR(IF('Paid Loss'!F11="","",'Paid Loss'!F11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="25">
+        <f>IFERROR(IF('Paid Loss'!G11="","",'Paid Loss'!G11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IFERROR(IF('Paid Loss'!H11="","",'Paid Loss'!H11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="25">
+        <f>IFERROR(IF('Paid Loss'!I11="","",'Paid Loss'!I11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="25">
+        <f>IFERROR(IF('Paid Loss'!J11="","",'Paid Loss'!J11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
+        <f>IFERROR(IF('Paid Loss'!K11="","",'Paid Loss'!K11/'Sel Ults - Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Paid Loss'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="25">
+        <f>IFERROR(IF('Paid Loss'!B12="","",'Paid Loss'!B12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="25">
+        <f>IFERROR(IF('Paid Loss'!C12="","",'Paid Loss'!C12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="25">
+        <f>IFERROR(IF('Paid Loss'!D12="","",'Paid Loss'!D12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>IFERROR(IF('Paid Loss'!E12="","",'Paid Loss'!E12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="25">
+        <f>IFERROR(IF('Paid Loss'!F12="","",'Paid Loss'!F12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="25">
+        <f>IFERROR(IF('Paid Loss'!G12="","",'Paid Loss'!G12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25">
+        <f>IFERROR(IF('Paid Loss'!H12="","",'Paid Loss'!H12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="25">
+        <f>IFERROR(IF('Paid Loss'!I12="","",'Paid Loss'!I12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="25">
+        <f>IFERROR(IF('Paid Loss'!J12="","",'Paid Loss'!J12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="25">
+        <f>IFERROR(IF('Paid Loss'!K12="","",'Paid Loss'!K12/'Sel Ults - Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Reported to Ultimate — ratio triangle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29">
+        <f>'Reported Count'!B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="29">
+        <f>'Reported Count'!C$2</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>'Reported Count'!D$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>'Reported Count'!E$2</f>
+        <v/>
+      </c>
+      <c r="F2" s="29">
+        <f>'Reported Count'!F$2</f>
+        <v/>
+      </c>
+      <c r="G2" s="29">
+        <f>'Reported Count'!G$2</f>
+        <v/>
+      </c>
+      <c r="H2" s="29">
+        <f>'Reported Count'!H$2</f>
+        <v/>
+      </c>
+      <c r="I2" s="29">
+        <f>'Reported Count'!I$2</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>'Reported Count'!J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>'Reported Count'!K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Reported Count'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="25">
+        <f>IFERROR(IF('Reported Count'!B3="","",'Reported Count'!B3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="25">
+        <f>IFERROR(IF('Reported Count'!C3="","",'Reported Count'!C3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="25">
+        <f>IFERROR(IF('Reported Count'!D3="","",'Reported Count'!D3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="25">
+        <f>IFERROR(IF('Reported Count'!E3="","",'Reported Count'!E3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="25">
+        <f>IFERROR(IF('Reported Count'!F3="","",'Reported Count'!F3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="25">
+        <f>IFERROR(IF('Reported Count'!G3="","",'Reported Count'!G3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="25">
+        <f>IFERROR(IF('Reported Count'!H3="","",'Reported Count'!H3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="25">
+        <f>IFERROR(IF('Reported Count'!I3="","",'Reported Count'!I3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="25">
+        <f>IFERROR(IF('Reported Count'!J3="","",'Reported Count'!J3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="25">
+        <f>IFERROR(IF('Reported Count'!K3="","",'Reported Count'!K3/'Sel Ults - Reported Count'!D3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Reported Count'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="25">
+        <f>IFERROR(IF('Reported Count'!B4="","",'Reported Count'!B4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="25">
+        <f>IFERROR(IF('Reported Count'!C4="","",'Reported Count'!C4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="25">
+        <f>IFERROR(IF('Reported Count'!D4="","",'Reported Count'!D4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="25">
+        <f>IFERROR(IF('Reported Count'!E4="","",'Reported Count'!E4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="25">
+        <f>IFERROR(IF('Reported Count'!F4="","",'Reported Count'!F4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="25">
+        <f>IFERROR(IF('Reported Count'!G4="","",'Reported Count'!G4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="25">
+        <f>IFERROR(IF('Reported Count'!H4="","",'Reported Count'!H4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="25">
+        <f>IFERROR(IF('Reported Count'!I4="","",'Reported Count'!I4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="25">
+        <f>IFERROR(IF('Reported Count'!J4="","",'Reported Count'!J4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="25">
+        <f>IFERROR(IF('Reported Count'!K4="","",'Reported Count'!K4/'Sel Ults - Reported Count'!D4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Reported Count'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="25">
+        <f>IFERROR(IF('Reported Count'!B5="","",'Reported Count'!B5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="25">
+        <f>IFERROR(IF('Reported Count'!C5="","",'Reported Count'!C5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="25">
+        <f>IFERROR(IF('Reported Count'!D5="","",'Reported Count'!D5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="25">
+        <f>IFERROR(IF('Reported Count'!E5="","",'Reported Count'!E5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="25">
+        <f>IFERROR(IF('Reported Count'!F5="","",'Reported Count'!F5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="25">
+        <f>IFERROR(IF('Reported Count'!G5="","",'Reported Count'!G5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25">
+        <f>IFERROR(IF('Reported Count'!H5="","",'Reported Count'!H5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="25">
+        <f>IFERROR(IF('Reported Count'!I5="","",'Reported Count'!I5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="25">
+        <f>IFERROR(IF('Reported Count'!J5="","",'Reported Count'!J5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
+        <f>IFERROR(IF('Reported Count'!K5="","",'Reported Count'!K5/'Sel Ults - Reported Count'!D5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Reported Count'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="25">
+        <f>IFERROR(IF('Reported Count'!B6="","",'Reported Count'!B6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="25">
+        <f>IFERROR(IF('Reported Count'!C6="","",'Reported Count'!C6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="25">
+        <f>IFERROR(IF('Reported Count'!D6="","",'Reported Count'!D6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IFERROR(IF('Reported Count'!E6="","",'Reported Count'!E6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>IFERROR(IF('Reported Count'!F6="","",'Reported Count'!F6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>IFERROR(IF('Reported Count'!G6="","",'Reported Count'!G6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>IFERROR(IF('Reported Count'!H6="","",'Reported Count'!H6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="25">
+        <f>IFERROR(IF('Reported Count'!I6="","",'Reported Count'!I6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="25">
+        <f>IFERROR(IF('Reported Count'!J6="","",'Reported Count'!J6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
+        <f>IFERROR(IF('Reported Count'!K6="","",'Reported Count'!K6/'Sel Ults - Reported Count'!D6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Reported Count'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="25">
+        <f>IFERROR(IF('Reported Count'!B7="","",'Reported Count'!B7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>IFERROR(IF('Reported Count'!C7="","",'Reported Count'!C7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>IFERROR(IF('Reported Count'!D7="","",'Reported Count'!D7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>IFERROR(IF('Reported Count'!E7="","",'Reported Count'!E7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>IFERROR(IF('Reported Count'!F7="","",'Reported Count'!F7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>IFERROR(IF('Reported Count'!G7="","",'Reported Count'!G7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>IFERROR(IF('Reported Count'!H7="","",'Reported Count'!H7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="25">
+        <f>IFERROR(IF('Reported Count'!I7="","",'Reported Count'!I7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>IFERROR(IF('Reported Count'!J7="","",'Reported Count'!J7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>IFERROR(IF('Reported Count'!K7="","",'Reported Count'!K7/'Sel Ults - Reported Count'!D7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Reported Count'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="25">
+        <f>IFERROR(IF('Reported Count'!B8="","",'Reported Count'!B8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="25">
+        <f>IFERROR(IF('Reported Count'!C8="","",'Reported Count'!C8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>IFERROR(IF('Reported Count'!D8="","",'Reported Count'!D8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IFERROR(IF('Reported Count'!E8="","",'Reported Count'!E8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>IFERROR(IF('Reported Count'!F8="","",'Reported Count'!F8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>IFERROR(IF('Reported Count'!G8="","",'Reported Count'!G8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IFERROR(IF('Reported Count'!H8="","",'Reported Count'!H8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>IFERROR(IF('Reported Count'!I8="","",'Reported Count'!I8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>IFERROR(IF('Reported Count'!J8="","",'Reported Count'!J8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
+        <f>IFERROR(IF('Reported Count'!K8="","",'Reported Count'!K8/'Sel Ults - Reported Count'!D8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Reported Count'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="25">
+        <f>IFERROR(IF('Reported Count'!B9="","",'Reported Count'!B9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>IFERROR(IF('Reported Count'!C9="","",'Reported Count'!C9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
+        <f>IFERROR(IF('Reported Count'!D9="","",'Reported Count'!D9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>IFERROR(IF('Reported Count'!E9="","",'Reported Count'!E9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>IFERROR(IF('Reported Count'!F9="","",'Reported Count'!F9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>IFERROR(IF('Reported Count'!G9="","",'Reported Count'!G9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>IFERROR(IF('Reported Count'!H9="","",'Reported Count'!H9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>IFERROR(IF('Reported Count'!I9="","",'Reported Count'!I9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="25">
+        <f>IFERROR(IF('Reported Count'!J9="","",'Reported Count'!J9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>IFERROR(IF('Reported Count'!K9="","",'Reported Count'!K9/'Sel Ults - Reported Count'!D9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Reported Count'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="25">
+        <f>IFERROR(IF('Reported Count'!B10="","",'Reported Count'!B10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="25">
+        <f>IFERROR(IF('Reported Count'!C10="","",'Reported Count'!C10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="25">
+        <f>IFERROR(IF('Reported Count'!D10="","",'Reported Count'!D10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>IFERROR(IF('Reported Count'!E10="","",'Reported Count'!E10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>IFERROR(IF('Reported Count'!F10="","",'Reported Count'!F10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>IFERROR(IF('Reported Count'!G10="","",'Reported Count'!G10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>IFERROR(IF('Reported Count'!H10="","",'Reported Count'!H10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="25">
+        <f>IFERROR(IF('Reported Count'!I10="","",'Reported Count'!I10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="25">
+        <f>IFERROR(IF('Reported Count'!J10="","",'Reported Count'!J10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="25">
+        <f>IFERROR(IF('Reported Count'!K10="","",'Reported Count'!K10/'Sel Ults - Reported Count'!D10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Reported Count'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="25">
+        <f>IFERROR(IF('Reported Count'!B11="","",'Reported Count'!B11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>IFERROR(IF('Reported Count'!C11="","",'Reported Count'!C11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="25">
+        <f>IFERROR(IF('Reported Count'!D11="","",'Reported Count'!D11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>IFERROR(IF('Reported Count'!E11="","",'Reported Count'!E11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
+        <f>IFERROR(IF('Reported Count'!F11="","",'Reported Count'!F11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="25">
+        <f>IFERROR(IF('Reported Count'!G11="","",'Reported Count'!G11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IFERROR(IF('Reported Count'!H11="","",'Reported Count'!H11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="25">
+        <f>IFERROR(IF('Reported Count'!I11="","",'Reported Count'!I11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="25">
+        <f>IFERROR(IF('Reported Count'!J11="","",'Reported Count'!J11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
+        <f>IFERROR(IF('Reported Count'!K11="","",'Reported Count'!K11/'Sel Ults - Reported Count'!D11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Reported Count'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="25">
+        <f>IFERROR(IF('Reported Count'!B12="","",'Reported Count'!B12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="25">
+        <f>IFERROR(IF('Reported Count'!C12="","",'Reported Count'!C12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="25">
+        <f>IFERROR(IF('Reported Count'!D12="","",'Reported Count'!D12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>IFERROR(IF('Reported Count'!E12="","",'Reported Count'!E12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="25">
+        <f>IFERROR(IF('Reported Count'!F12="","",'Reported Count'!F12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="25">
+        <f>IFERROR(IF('Reported Count'!G12="","",'Reported Count'!G12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25">
+        <f>IFERROR(IF('Reported Count'!H12="","",'Reported Count'!H12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="25">
+        <f>IFERROR(IF('Reported Count'!I12="","",'Reported Count'!I12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="25">
+        <f>IFERROR(IF('Reported Count'!J12="","",'Reported Count'!J12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="25">
+        <f>IFERROR(IF('Reported Count'!K12="","",'Reported Count'!K12/'Sel Ults - Reported Count'!D12),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Closed to Ultimate — ratio triangle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29">
+        <f>'Closed Count'!B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="29">
+        <f>'Closed Count'!C$2</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>'Closed Count'!D$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>'Closed Count'!E$2</f>
+        <v/>
+      </c>
+      <c r="F2" s="29">
+        <f>'Closed Count'!F$2</f>
+        <v/>
+      </c>
+      <c r="G2" s="29">
+        <f>'Closed Count'!G$2</f>
+        <v/>
+      </c>
+      <c r="H2" s="29">
+        <f>'Closed Count'!H$2</f>
+        <v/>
+      </c>
+      <c r="I2" s="29">
+        <f>'Closed Count'!I$2</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>'Closed Count'!J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>'Closed Count'!K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Closed Count'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="25">
+        <f>IFERROR(IF('Closed Count'!B3="","",'Closed Count'!B3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="25">
+        <f>IFERROR(IF('Closed Count'!C3="","",'Closed Count'!C3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="25">
+        <f>IFERROR(IF('Closed Count'!D3="","",'Closed Count'!D3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="25">
+        <f>IFERROR(IF('Closed Count'!E3="","",'Closed Count'!E3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="25">
+        <f>IFERROR(IF('Closed Count'!F3="","",'Closed Count'!F3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="25">
+        <f>IFERROR(IF('Closed Count'!G3="","",'Closed Count'!G3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="25">
+        <f>IFERROR(IF('Closed Count'!H3="","",'Closed Count'!H3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="25">
+        <f>IFERROR(IF('Closed Count'!I3="","",'Closed Count'!I3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="25">
+        <f>IFERROR(IF('Closed Count'!J3="","",'Closed Count'!J3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="25">
+        <f>IFERROR(IF('Closed Count'!K3="","",'Closed Count'!K3/'Sel Ults - Closed Count'!D3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Closed Count'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="25">
+        <f>IFERROR(IF('Closed Count'!B4="","",'Closed Count'!B4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="25">
+        <f>IFERROR(IF('Closed Count'!C4="","",'Closed Count'!C4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="25">
+        <f>IFERROR(IF('Closed Count'!D4="","",'Closed Count'!D4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="25">
+        <f>IFERROR(IF('Closed Count'!E4="","",'Closed Count'!E4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="25">
+        <f>IFERROR(IF('Closed Count'!F4="","",'Closed Count'!F4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="25">
+        <f>IFERROR(IF('Closed Count'!G4="","",'Closed Count'!G4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="25">
+        <f>IFERROR(IF('Closed Count'!H4="","",'Closed Count'!H4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="25">
+        <f>IFERROR(IF('Closed Count'!I4="","",'Closed Count'!I4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="25">
+        <f>IFERROR(IF('Closed Count'!J4="","",'Closed Count'!J4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="25">
+        <f>IFERROR(IF('Closed Count'!K4="","",'Closed Count'!K4/'Sel Ults - Closed Count'!D4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Closed Count'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="25">
+        <f>IFERROR(IF('Closed Count'!B5="","",'Closed Count'!B5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="25">
+        <f>IFERROR(IF('Closed Count'!C5="","",'Closed Count'!C5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="25">
+        <f>IFERROR(IF('Closed Count'!D5="","",'Closed Count'!D5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="25">
+        <f>IFERROR(IF('Closed Count'!E5="","",'Closed Count'!E5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="25">
+        <f>IFERROR(IF('Closed Count'!F5="","",'Closed Count'!F5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="25">
+        <f>IFERROR(IF('Closed Count'!G5="","",'Closed Count'!G5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25">
+        <f>IFERROR(IF('Closed Count'!H5="","",'Closed Count'!H5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="25">
+        <f>IFERROR(IF('Closed Count'!I5="","",'Closed Count'!I5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="25">
+        <f>IFERROR(IF('Closed Count'!J5="","",'Closed Count'!J5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
+        <f>IFERROR(IF('Closed Count'!K5="","",'Closed Count'!K5/'Sel Ults - Closed Count'!D5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Closed Count'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="25">
+        <f>IFERROR(IF('Closed Count'!B6="","",'Closed Count'!B6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="25">
+        <f>IFERROR(IF('Closed Count'!C6="","",'Closed Count'!C6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="25">
+        <f>IFERROR(IF('Closed Count'!D6="","",'Closed Count'!D6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IFERROR(IF('Closed Count'!E6="","",'Closed Count'!E6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>IFERROR(IF('Closed Count'!F6="","",'Closed Count'!F6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>IFERROR(IF('Closed Count'!G6="","",'Closed Count'!G6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>IFERROR(IF('Closed Count'!H6="","",'Closed Count'!H6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="25">
+        <f>IFERROR(IF('Closed Count'!I6="","",'Closed Count'!I6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="25">
+        <f>IFERROR(IF('Closed Count'!J6="","",'Closed Count'!J6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
+        <f>IFERROR(IF('Closed Count'!K6="","",'Closed Count'!K6/'Sel Ults - Closed Count'!D6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Closed Count'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="25">
+        <f>IFERROR(IF('Closed Count'!B7="","",'Closed Count'!B7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>IFERROR(IF('Closed Count'!C7="","",'Closed Count'!C7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>IFERROR(IF('Closed Count'!D7="","",'Closed Count'!D7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>IFERROR(IF('Closed Count'!E7="","",'Closed Count'!E7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>IFERROR(IF('Closed Count'!F7="","",'Closed Count'!F7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>IFERROR(IF('Closed Count'!G7="","",'Closed Count'!G7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>IFERROR(IF('Closed Count'!H7="","",'Closed Count'!H7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="25">
+        <f>IFERROR(IF('Closed Count'!I7="","",'Closed Count'!I7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>IFERROR(IF('Closed Count'!J7="","",'Closed Count'!J7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>IFERROR(IF('Closed Count'!K7="","",'Closed Count'!K7/'Sel Ults - Closed Count'!D7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Closed Count'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="25">
+        <f>IFERROR(IF('Closed Count'!B8="","",'Closed Count'!B8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="25">
+        <f>IFERROR(IF('Closed Count'!C8="","",'Closed Count'!C8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>IFERROR(IF('Closed Count'!D8="","",'Closed Count'!D8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IFERROR(IF('Closed Count'!E8="","",'Closed Count'!E8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>IFERROR(IF('Closed Count'!F8="","",'Closed Count'!F8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>IFERROR(IF('Closed Count'!G8="","",'Closed Count'!G8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>IFERROR(IF('Closed Count'!H8="","",'Closed Count'!H8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>IFERROR(IF('Closed Count'!I8="","",'Closed Count'!I8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>IFERROR(IF('Closed Count'!J8="","",'Closed Count'!J8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
+        <f>IFERROR(IF('Closed Count'!K8="","",'Closed Count'!K8/'Sel Ults - Closed Count'!D8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Closed Count'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="25">
+        <f>IFERROR(IF('Closed Count'!B9="","",'Closed Count'!B9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>IFERROR(IF('Closed Count'!C9="","",'Closed Count'!C9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
+        <f>IFERROR(IF('Closed Count'!D9="","",'Closed Count'!D9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>IFERROR(IF('Closed Count'!E9="","",'Closed Count'!E9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>IFERROR(IF('Closed Count'!F9="","",'Closed Count'!F9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>IFERROR(IF('Closed Count'!G9="","",'Closed Count'!G9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>IFERROR(IF('Closed Count'!H9="","",'Closed Count'!H9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>IFERROR(IF('Closed Count'!I9="","",'Closed Count'!I9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="25">
+        <f>IFERROR(IF('Closed Count'!J9="","",'Closed Count'!J9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>IFERROR(IF('Closed Count'!K9="","",'Closed Count'!K9/'Sel Ults - Closed Count'!D9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Closed Count'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="25">
+        <f>IFERROR(IF('Closed Count'!B10="","",'Closed Count'!B10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="25">
+        <f>IFERROR(IF('Closed Count'!C10="","",'Closed Count'!C10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="25">
+        <f>IFERROR(IF('Closed Count'!D10="","",'Closed Count'!D10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>IFERROR(IF('Closed Count'!E10="","",'Closed Count'!E10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>IFERROR(IF('Closed Count'!F10="","",'Closed Count'!F10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>IFERROR(IF('Closed Count'!G10="","",'Closed Count'!G10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25">
+        <f>IFERROR(IF('Closed Count'!H10="","",'Closed Count'!H10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="25">
+        <f>IFERROR(IF('Closed Count'!I10="","",'Closed Count'!I10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="25">
+        <f>IFERROR(IF('Closed Count'!J10="","",'Closed Count'!J10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="25">
+        <f>IFERROR(IF('Closed Count'!K10="","",'Closed Count'!K10/'Sel Ults - Closed Count'!D10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Closed Count'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="25">
+        <f>IFERROR(IF('Closed Count'!B11="","",'Closed Count'!B11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>IFERROR(IF('Closed Count'!C11="","",'Closed Count'!C11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="25">
+        <f>IFERROR(IF('Closed Count'!D11="","",'Closed Count'!D11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>IFERROR(IF('Closed Count'!E11="","",'Closed Count'!E11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
+        <f>IFERROR(IF('Closed Count'!F11="","",'Closed Count'!F11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="25">
+        <f>IFERROR(IF('Closed Count'!G11="","",'Closed Count'!G11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25">
+        <f>IFERROR(IF('Closed Count'!H11="","",'Closed Count'!H11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="25">
+        <f>IFERROR(IF('Closed Count'!I11="","",'Closed Count'!I11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="25">
+        <f>IFERROR(IF('Closed Count'!J11="","",'Closed Count'!J11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="25">
+        <f>IFERROR(IF('Closed Count'!K11="","",'Closed Count'!K11/'Sel Ults - Closed Count'!D11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Closed Count'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="25">
+        <f>IFERROR(IF('Closed Count'!B12="","",'Closed Count'!B12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="25">
+        <f>IFERROR(IF('Closed Count'!C12="","",'Closed Count'!C12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="25">
+        <f>IFERROR(IF('Closed Count'!D12="","",'Closed Count'!D12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>IFERROR(IF('Closed Count'!E12="","",'Closed Count'!E12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="25">
+        <f>IFERROR(IF('Closed Count'!F12="","",'Closed Count'!F12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="25">
+        <f>IFERROR(IF('Closed Count'!G12="","",'Closed Count'!G12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25">
+        <f>IFERROR(IF('Closed Count'!H12="","",'Closed Count'!H12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="25">
+        <f>IFERROR(IF('Closed Count'!I12="","",'Closed Count'!I12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="25">
+        <f>IFERROR(IF('Closed Count'!J12="","",'Closed Count'!J12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="25">
+        <f>IFERROR(IF('Closed Count'!K12="","",'Closed Count'!K12/'Sel Ults - Closed Count'!D12),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Average IBNR (Incurred Ult - Incurred)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29">
+        <f>'Incurred Loss'!B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="29">
+        <f>'Incurred Loss'!C$2</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>'Incurred Loss'!D$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>'Incurred Loss'!E$2</f>
+        <v/>
+      </c>
+      <c r="F2" s="29">
+        <f>'Incurred Loss'!F$2</f>
+        <v/>
+      </c>
+      <c r="G2" s="29">
+        <f>'Incurred Loss'!G$2</f>
+        <v/>
+      </c>
+      <c r="H2" s="29">
+        <f>'Incurred Loss'!H$2</f>
+        <v/>
+      </c>
+      <c r="I2" s="29">
+        <f>'Incurred Loss'!I$2</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>'Incurred Loss'!J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>'Incurred Loss'!K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Incurred Loss'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!B3),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!C3),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!E3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!F3),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!G3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!H3),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!I3),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!J3),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K3="","",'Sel Ults - Incurred Loss'!D3-'Incurred Loss'!K3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Incurred Loss'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!B4),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!C4),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!E4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!F4),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!G4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!H4),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!I4),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!J4),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K4="","",'Sel Ults - Incurred Loss'!D4-'Incurred Loss'!K4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Incurred Loss'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!B5),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!C5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!E5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!F5),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!G5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!H5),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!I5),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!J5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K5="","",'Sel Ults - Incurred Loss'!D5-'Incurred Loss'!K5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Incurred Loss'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!B6),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!C6),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!E6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!F6),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!G6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!H6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!I6),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!J6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K6="","",'Sel Ults - Incurred Loss'!D6-'Incurred Loss'!K6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Incurred Loss'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!B7),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!C7),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!E7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!F7),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!G7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!H7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!I7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!J7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K7="","",'Sel Ults - Incurred Loss'!D7-'Incurred Loss'!K7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Incurred Loss'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!B8),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!C8),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!E8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!F8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!G8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!H8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!I8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!J8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K8="","",'Sel Ults - Incurred Loss'!D8-'Incurred Loss'!K8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Incurred Loss'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!B9),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!C9),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!E9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!F9),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!G9),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!H9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!I9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!J9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K9="","",'Sel Ults - Incurred Loss'!D9-'Incurred Loss'!K9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Incurred Loss'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!B10),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!C10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!E10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!F10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!G10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!H10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!I10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!J10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K10="","",'Sel Ults - Incurred Loss'!D10-'Incurred Loss'!K10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Incurred Loss'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!B11),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!C11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!E11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!F11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!G11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!H11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!I11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!J11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K11="","",'Sel Ults - Incurred Loss'!D11-'Incurred Loss'!K11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Incurred Loss'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!B12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!B12),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!C12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!C12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!D12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!E12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!E12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!F12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!F12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!G12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!G12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!H12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!H12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!I12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!I12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!J12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!J12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="27">
+        <f>IFERROR(IF('Incurred Loss'!K12="","",'Sel Ults - Incurred Loss'!D12-'Incurred Loss'!K12),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Average Unpaid (Incurred Ult - Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B2" s="29">
+        <f>'Incurred Loss'!B$2</f>
+        <v/>
+      </c>
+      <c r="C2" s="29">
+        <f>'Incurred Loss'!C$2</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>'Incurred Loss'!D$2</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>'Incurred Loss'!E$2</f>
+        <v/>
+      </c>
+      <c r="F2" s="29">
+        <f>'Incurred Loss'!F$2</f>
+        <v/>
+      </c>
+      <c r="G2" s="29">
+        <f>'Incurred Loss'!G$2</f>
+        <v/>
+      </c>
+      <c r="H2" s="29">
+        <f>'Incurred Loss'!H$2</f>
+        <v/>
+      </c>
+      <c r="I2" s="29">
+        <f>'Incurred Loss'!I$2</f>
+        <v/>
+      </c>
+      <c r="J2" s="29">
+        <f>'Incurred Loss'!J$2</f>
+        <v/>
+      </c>
+      <c r="K2" s="29">
+        <f>'Incurred Loss'!K$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>'Incurred Loss'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="27">
+        <f>IFERROR(IF('Paid Loss'!B3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!B3),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="27">
+        <f>IFERROR(IF('Paid Loss'!C3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!C3),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="27">
+        <f>IFERROR(IF('Paid Loss'!D3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!D3),"")</f>
+        <v/>
+      </c>
+      <c r="E3" s="27">
+        <f>IFERROR(IF('Paid Loss'!E3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!E3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="27">
+        <f>IFERROR(IF('Paid Loss'!F3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!F3),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="27">
+        <f>IFERROR(IF('Paid Loss'!G3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!G3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="27">
+        <f>IFERROR(IF('Paid Loss'!H3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!H3),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="27">
+        <f>IFERROR(IF('Paid Loss'!I3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!I3),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="27">
+        <f>IFERROR(IF('Paid Loss'!J3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!J3),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="27">
+        <f>IFERROR(IF('Paid Loss'!K3="","",'Sel Ults - Incurred Loss'!D3-'Paid Loss'!K3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>'Incurred Loss'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="27">
+        <f>IFERROR(IF('Paid Loss'!B4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!B4),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="27">
+        <f>IFERROR(IF('Paid Loss'!C4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!C4),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="27">
+        <f>IFERROR(IF('Paid Loss'!D4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!D4),"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="27">
+        <f>IFERROR(IF('Paid Loss'!E4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!E4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="27">
+        <f>IFERROR(IF('Paid Loss'!F4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!F4),"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="27">
+        <f>IFERROR(IF('Paid Loss'!G4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!G4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="27">
+        <f>IFERROR(IF('Paid Loss'!H4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!H4),"")</f>
+        <v/>
+      </c>
+      <c r="I4" s="27">
+        <f>IFERROR(IF('Paid Loss'!I4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!I4),"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="27">
+        <f>IFERROR(IF('Paid Loss'!J4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!J4),"")</f>
+        <v/>
+      </c>
+      <c r="K4" s="27">
+        <f>IFERROR(IF('Paid Loss'!K4="","",'Sel Ults - Incurred Loss'!D4-'Paid Loss'!K4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <f>'Incurred Loss'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="27">
+        <f>IFERROR(IF('Paid Loss'!B5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!B5),"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="27">
+        <f>IFERROR(IF('Paid Loss'!C5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!C5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="27">
+        <f>IFERROR(IF('Paid Loss'!D5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!D5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="27">
+        <f>IFERROR(IF('Paid Loss'!E5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!E5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="27">
+        <f>IFERROR(IF('Paid Loss'!F5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!F5),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="27">
+        <f>IFERROR(IF('Paid Loss'!G5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!G5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="27">
+        <f>IFERROR(IF('Paid Loss'!H5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!H5),"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="27">
+        <f>IFERROR(IF('Paid Loss'!I5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!I5),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="27">
+        <f>IFERROR(IF('Paid Loss'!J5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!J5),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="27">
+        <f>IFERROR(IF('Paid Loss'!K5="","",'Sel Ults - Incurred Loss'!D5-'Paid Loss'!K5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <f>'Incurred Loss'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="27">
+        <f>IFERROR(IF('Paid Loss'!B6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!B6),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="27">
+        <f>IFERROR(IF('Paid Loss'!C6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!C6),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="27">
+        <f>IFERROR(IF('Paid Loss'!D6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!D6),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>IFERROR(IF('Paid Loss'!E6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!E6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="27">
+        <f>IFERROR(IF('Paid Loss'!F6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!F6),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="27">
+        <f>IFERROR(IF('Paid Loss'!G6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!G6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="27">
+        <f>IFERROR(IF('Paid Loss'!H6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!H6),"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="27">
+        <f>IFERROR(IF('Paid Loss'!I6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!I6),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="27">
+        <f>IFERROR(IF('Paid Loss'!J6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!J6),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="27">
+        <f>IFERROR(IF('Paid Loss'!K6="","",'Sel Ults - Incurred Loss'!D6-'Paid Loss'!K6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <f>'Incurred Loss'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="27">
+        <f>IFERROR(IF('Paid Loss'!B7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!B7),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="27">
+        <f>IFERROR(IF('Paid Loss'!C7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!C7),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="27">
+        <f>IFERROR(IF('Paid Loss'!D7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!D7),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="27">
+        <f>IFERROR(IF('Paid Loss'!E7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!E7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="27">
+        <f>IFERROR(IF('Paid Loss'!F7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!F7),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>IFERROR(IF('Paid Loss'!G7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!G7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="27">
+        <f>IFERROR(IF('Paid Loss'!H7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!H7),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="27">
+        <f>IFERROR(IF('Paid Loss'!I7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!I7),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="27">
+        <f>IFERROR(IF('Paid Loss'!J7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!J7),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="27">
+        <f>IFERROR(IF('Paid Loss'!K7="","",'Sel Ults - Incurred Loss'!D7-'Paid Loss'!K7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <f>'Incurred Loss'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="27">
+        <f>IFERROR(IF('Paid Loss'!B8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!B8),"")</f>
+        <v/>
+      </c>
+      <c r="C8" s="27">
+        <f>IFERROR(IF('Paid Loss'!C8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!C8),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="27">
+        <f>IFERROR(IF('Paid Loss'!D8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!D8),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>IFERROR(IF('Paid Loss'!E8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!E8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="27">
+        <f>IFERROR(IF('Paid Loss'!F8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!F8),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>IFERROR(IF('Paid Loss'!G8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!G8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="27">
+        <f>IFERROR(IF('Paid Loss'!H8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!H8),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="27">
+        <f>IFERROR(IF('Paid Loss'!I8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!I8),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="27">
+        <f>IFERROR(IF('Paid Loss'!J8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!J8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="27">
+        <f>IFERROR(IF('Paid Loss'!K8="","",'Sel Ults - Incurred Loss'!D8-'Paid Loss'!K8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>'Incurred Loss'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="27">
+        <f>IFERROR(IF('Paid Loss'!B9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!B9),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="27">
+        <f>IFERROR(IF('Paid Loss'!C9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!C9),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>IFERROR(IF('Paid Loss'!D9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!D9),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="27">
+        <f>IFERROR(IF('Paid Loss'!E9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!E9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>IFERROR(IF('Paid Loss'!F9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!F9),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
+        <f>IFERROR(IF('Paid Loss'!G9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!G9),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="27">
+        <f>IFERROR(IF('Paid Loss'!H9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!H9),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="27">
+        <f>IFERROR(IF('Paid Loss'!I9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!I9),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="27">
+        <f>IFERROR(IF('Paid Loss'!J9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!J9),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="27">
+        <f>IFERROR(IF('Paid Loss'!K9="","",'Sel Ults - Incurred Loss'!D9-'Paid Loss'!K9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>'Incurred Loss'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="27">
+        <f>IFERROR(IF('Paid Loss'!B10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!B10),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>IFERROR(IF('Paid Loss'!C10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!C10),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>IFERROR(IF('Paid Loss'!D10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!D10),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>IFERROR(IF('Paid Loss'!E10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!E10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>IFERROR(IF('Paid Loss'!F10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!F10),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>IFERROR(IF('Paid Loss'!G10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!G10),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="27">
+        <f>IFERROR(IF('Paid Loss'!H10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!H10),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="27">
+        <f>IFERROR(IF('Paid Loss'!I10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!I10),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="27">
+        <f>IFERROR(IF('Paid Loss'!J10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!J10),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="27">
+        <f>IFERROR(IF('Paid Loss'!K10="","",'Sel Ults - Incurred Loss'!D10-'Paid Loss'!K10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>'Incurred Loss'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="27">
+        <f>IFERROR(IF('Paid Loss'!B11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!B11),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="27">
+        <f>IFERROR(IF('Paid Loss'!C11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!C11),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>IFERROR(IF('Paid Loss'!D11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!D11),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>IFERROR(IF('Paid Loss'!E11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!E11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>IFERROR(IF('Paid Loss'!F11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!F11),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="27">
+        <f>IFERROR(IF('Paid Loss'!G11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!G11),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="27">
+        <f>IFERROR(IF('Paid Loss'!H11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!H11),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="27">
+        <f>IFERROR(IF('Paid Loss'!I11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!I11),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="27">
+        <f>IFERROR(IF('Paid Loss'!J11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!J11),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="27">
+        <f>IFERROR(IF('Paid Loss'!K11="","",'Sel Ults - Incurred Loss'!D11-'Paid Loss'!K11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>'Incurred Loss'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="27">
+        <f>IFERROR(IF('Paid Loss'!B12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!B12),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>IFERROR(IF('Paid Loss'!C12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!C12),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>IFERROR(IF('Paid Loss'!D12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!D12),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>IFERROR(IF('Paid Loss'!E12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!E12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>IFERROR(IF('Paid Loss'!F12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!F12),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>IFERROR(IF('Paid Loss'!G12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!G12),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>IFERROR(IF('Paid Loss'!H12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!H12),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>IFERROR(IF('Paid Loss'!I12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!I12),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="27">
+        <f>IFERROR(IF('Paid Loss'!J12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!J12),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="27">
+        <f>IFERROR(IF('Paid Loss'!K12="","",'Sel Ults - Incurred Loss'!D12-'Paid Loss'!K12),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
